--- a/Work/Регистрация/2026-10-19 2-х дневный семинар Сумма технологииСанкт-Петербург 2425 окт.xlsx
+++ b/Work/Регистрация/2026-10-19 2-х дневный семинар Сумма технологииСанкт-Петербург 2425 окт.xlsx
@@ -744,6 +744,229 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2562152747</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:12:45</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-10-19 23:19:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Алексей Карпов</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>9639310@gmail.com</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>+79219639310</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>QR-кодом</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2562191205</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:09:16</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-10-20 01:02:13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>910377</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Федоров</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>tsak.ru@gmail.com</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>+79219731807</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>QR-кодом</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Один</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2562270622</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:10:12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:12:16</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Кобленц Павел</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pkoblents@gmail.com</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>+79669255015</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Один</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Work/Регистрация/2026-10-19 2-х дневный семинар Сумма технологииСанкт-Петербург 2425 окт.xlsx
+++ b/Work/Регистрация/2026-10-19 2-х дневный семинар Сумма технологииСанкт-Петербург 2425 окт.xlsx
@@ -423,95 +423,75 @@
     <row r="1" customFormat="1" s="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>Имя и фамилия [1]</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Время начала заполнения формы</t>
+          <t>E-mail [1]</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Время создания</t>
+          <t>Ваш телефон [1]</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Время затраченное на заполнение формы</t>
+          <t>Билет [1]</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Имя и фамилия [1]</t>
+          <t>У меня есть скидка (впишите скидку и комментарий: "от кого" [1]</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>E-mail [1]</t>
+          <t>Хочу оплатить: [1]</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Ваш телефон [1]</t>
+          <t>Комментарий (в каком составе прибудете на встречу) [1]</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Билет [1]</t>
+          <t>ВХОДНЫМ БИЛЕТОМ ЯВЛЯЕТСЯ ФОТО ЧЕКА ОПЛАТЫ. Подтверждаю. [1]</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>У меня есть скидка (впишите скидку и комментарий: "от кого" [1]</t>
+          <t>Согласны на обработку персональных данных? [1]</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Хочу оплатить: [1]</t>
+          <t>Откуда вы узнали о семинаре? / Реклама ВКонтакте</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Комментарий (в каком составе прибудете на встречу) [1]</t>
+          <t>Откуда вы узнали о семинаре? / Группа ВКонтакте</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ВХОДНЫМ БИЛЕТОМ ЯВЛЯЕТСЯ ФОТО ЧЕКА ОПЛАТЫ. Подтверждаю. [1]</t>
+          <t>Откуда вы узнали о семинаре? / Telegram-канал</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Согласны на обработку персональных данных? [1]</t>
+          <t>Откуда вы узнали о семинаре? / Leader-ID</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Откуда вы узнали о семинаре? / Реклама ВКонтакте</t>
+          <t>Откуда вы узнали о семинаре? / Ссылки с других сайтов и каналов</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
-        <is>
-          <t>Откуда вы узнали о семинаре? / Группа ВКонтакте</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Откуда вы узнали о семинаре? / Telegram-канал</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Откуда вы узнали о семинаре? / Leader-ID</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>Откуда вы узнали о семинаре? / Ссылки с других сайтов и каналов</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>Откуда вы узнали о семинаре? / От друзей и коллег</t>
         </is>
@@ -520,148 +500,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2550798006</t>
+          <t>Иван Петров</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-10 11:07:45</t>
+          <t>12345@1222.com</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-10 11:18:06</t>
+          <t>1234567</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>До 20 лет — бесплатно</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Иван Петров</t>
+          <t>Это тест. Проверка работоспособности сайта</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12345@1222.com</t>
+          <t>Наличными на семинаре</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1234567</t>
+          <t>один</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>До 20 лет — бесплатно</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Это тест. Проверка работоспособности сайта</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Наличными на семинаре</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>один</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2561196299</t>
+          <t>Людмила Квартальнова</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-19 11:22:00</t>
+          <t>klv1907@yandex.ru</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-19 11:26:44</t>
+          <t>+79117412791</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Людмила Квартальнова</t>
+          <t>Технология смысла</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>klv1907@yandex.ru</t>
+          <t>Наличными на семинаре</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+79117412791</t>
+          <t xml:space="preserve">Надеюсь, что с подругой. </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Технология смысла</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Наличными на семинаре</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Надеюсь, что с подругой. </t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>От друзей и коллег</t>
         </is>
@@ -670,75 +610,55 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2561625723</t>
+          <t>Александр Струцинский</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:39:48</t>
+          <t>poplavok@inbox.ru</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-19 15:47:12</t>
+          <t>+7(965)143-0471</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Александр Струцинский</t>
+          <t>тестовое заполнение</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>poplavok@inbox.ru</t>
+          <t>Другим способом (напишите на почту:  kedrpiter@ya.ru)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+7(965)143-0471</t>
+          <t>тестовое заполнение</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Друзьям и учредителям семинара — скидка 50%</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>тестовое заполнение</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Другим способом (напишите на почту:  kedrpiter@ya.ru)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>тестовое заполнение</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>От друзей и коллег</t>
         </is>
@@ -747,71 +667,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2562152747</t>
+          <t>Алексей Карпов</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19 23:12:45</t>
+          <t>9639310@gmail.com</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-10-19 23:19:00</t>
+          <t>+79219639310</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Алексей Карпов</t>
-        </is>
-      </c>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9639310@gmail.com</t>
+          <t>QR-кодом</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+79219639310</t>
+          <t>Да</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Друзьям и учредителям семинара — скидка 50%</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>QR-кодом</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>От друзей и коллег</t>
         </is>
@@ -820,75 +720,55 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2562191205</t>
+          <t>Федоров</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-09 12:09:16</t>
+          <t>tsak.ru@gmail.com</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-10-20 01:02:13</t>
+          <t>+79219731807</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>910377</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Федоров</t>
-        </is>
-      </c>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>tsak.ru@gmail.com</t>
+          <t>QR-кодом</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+79219731807</t>
+          <t>Один</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Друзьям и учредителям семинара — скидка 50%</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>QR-кодом</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Один</t>
-        </is>
-      </c>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Telegram-канал</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>От друзей и коллег</t>
         </is>
@@ -897,75 +777,503 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2562270622</t>
+          <t>Кобленц Павел</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 06:10:12</t>
+          <t>Pkoblents@gmail.com</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-10-20 06:12:16</t>
+          <t>+79669255015</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Кобленц Павел</t>
-        </is>
-      </c>
+          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pkoblents@gmail.com</t>
+          <t>Наличными на семинаре</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+79669255015</t>
+          <t>Один</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Максим Сурин</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>uloxvk@gmail.com</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>89817713200</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>До 20 лет — бесплатно</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Лично</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Кирилл Аникин</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mr.kirillanikin@yandex.ru</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>+79681934474</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>До 20 лет — бесплатно</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Лично</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Платон Кузьмин</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Valio.spb@mail.ru</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>+79119656789</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Это Платон, пиведу ещё Олежку, пригласил Станислав</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Наличными на семинаре</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Один</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Да</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Олежка знал Андрейчика и Эмирчика.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Oleg Fedorov</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>i@webseodev.ru</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>+79119119946</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>От друзей и коллег</t>
         </is>
       </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Олег</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>i@webseodev.ru</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>+79119119964</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Пакет на оба дня — 3000 ₽ (выгода 2000 ₽)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Потапов Дмитрий</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>dn-potapov@yandex,ru</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>+7 911 939 5768</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Организатор, спикер - бесплатно</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Другим способом (напишите на почту:  kedrpiter@ya.ru)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>один с докладом</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Группа ВКонтакте</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Анастасия Куценко </t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>asya.kycenko@gmail.com</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>9119086931</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>От друзей и коллег</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Белов Леонид</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>bel.new@mail.ru</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>+7911 2442848</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Друзьям и учредителям семинара — скидка 50%</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>от Станислава Смирнова</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Наличными на семинаре</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>персонально</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Telegram-канал</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
